--- a/data/trans_orig/KIDM_C_1_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/KIDM_C_1_R-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen muchos o muchísimos problemas para dormir (autopercepción menor) en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores que tienen muchos o muchísimos problemas para dormir (autopercepción menor) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>826</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7903</t>
+          <t>7372</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4052</t>
+          <t>4408</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14578</t>
+          <t>15870</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>6397</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18598</t>
+          <t>18806</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60022</t>
+          <t>60553</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67090</t>
+          <t>67099</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>84787</t>
+          <t>83495</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>95313</t>
+          <t>94957</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>148692</t>
+          <t>148484</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>160799</t>
+          <t>160893</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,18%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>3305</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15778</t>
+          <t>15376</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>918</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7940</t>
+          <t>8820</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6450</t>
+          <t>6470</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19842</t>
+          <t>19591</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>126769</t>
+          <t>127171</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>139234</t>
+          <t>139242</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>164843</t>
+          <t>163963</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>171952</t>
+          <t>171865</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>295487</t>
+          <t>295738</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>308879</t>
+          <t>308859</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5677</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18714</t>
+          <t>18666</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6712</t>
+          <t>6303</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20753</t>
+          <t>19461</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14774</t>
+          <t>14634</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32497</t>
+          <t>33181</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>191758</t>
+          <t>191806</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>204795</t>
+          <t>204302</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>251394</t>
+          <t>252686</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>265435</t>
+          <t>265844</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>450122</t>
+          <t>449438</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>467845</t>
+          <t>467985</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,97%</t>
         </is>
       </c>
     </row>
